--- a/examples/demo/demo_workbook.xlsx
+++ b/examples/demo/demo_workbook.xlsx
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="H3" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="17" t="inlineStr">
         <is>

--- a/examples/demo/demo_workbook.xlsx
+++ b/examples/demo/demo_workbook.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11.83" customWidth="1" style="11" min="1" max="1"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>EngineData</t>
+          <t>VehicleDynamics</t>
         </is>
       </c>
       <c r="C2" s="15" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="D2" s="14" t="inlineStr">
         <is>
-          <t>EngineSpeed</t>
+          <t>VehicleSpeed</t>
         </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
@@ -571,220 +571,850 @@
       </c>
       <c r="I2" s="15" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J2" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>655.35</t>
+        </is>
+      </c>
+      <c r="M2" s="14" t="inlineStr">
+        <is>
+          <t>kph</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="12">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>0x100</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>VehicleDynamics</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Acceleration</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>little_endian</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" s="15" t="inlineStr">
+        <is>
+          <t>-32.768</t>
+        </is>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>32.767</t>
+        </is>
+      </c>
+      <c r="M3" s="14" t="inlineStr">
+        <is>
+          <t>m/s2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="12">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>BrakeStatus</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>BrakePressure</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>little_endian</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>6553.5</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>kPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="12">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>BrakeStatus</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>BrakeActive</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>little_endian</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" s="14" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>0x300</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Powertrain</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>EngineRPM</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>little_endian</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="J2" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" s="15" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="M2" s="14" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>16383.75</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
         <is>
           <t>rpm</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="12">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>0x100</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>EngineData</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>0x300</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Powertrain</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>EngineTemp</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>CoolantTemp</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>little_endian</t>
         </is>
       </c>
-      <c r="H3" s="16" t="b">
+      <c r="H7" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="I3" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="K3" s="17" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L7" s="15" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="M3" s="16" t="inlineStr">
+      <c r="M7" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="12">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>BrakeStatus</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>0x300</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Powertrain</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>BrakePressure</t>
-        </is>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Ignition</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>little_endian</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>0x300</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Powertrain</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>FaultCode</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>little_endian</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="15" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="M9" s="14" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>0x310</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>BodyStatus</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>BatteryVoltage</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>little_endian</t>
         </is>
       </c>
-      <c r="H4" s="19" t="b">
+      <c r="H10" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="I4" s="18" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="18" t="inlineStr">
-        <is>
-          <t>6553.5</t>
-        </is>
-      </c>
-      <c r="M4" s="19" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="12">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>BrakeStatus</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="15" t="inlineStr">
+        <is>
+          <t>655.35</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>0x310</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>BodyStatus</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>BrakeActive</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>ParkingBrake</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>little_endian</t>
         </is>
       </c>
-      <c r="H5" s="19" t="b">
+      <c r="H11" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" s="19" t="n"/>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>0x310</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>BodyStatus</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>BrakePedal</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>little_endian</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>0x310</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>BodyStatus</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>BrakeLight</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>little_endian</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>0x310</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>BodyStatus</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>FuelLevel</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>little_endian</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>0x310</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>BodyStatus</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>FuelWarning</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>little_endian</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1058,7 +1688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13.65" customWidth="1" style="11" min="1" max="1"/>
@@ -1281,6 +1911,55 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Brake response</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>BrakePressure</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>exceeds</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>BrakeActive</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>equals</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="21" t="n"/>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
